--- a/results/For_Others/Phil_Tassi/Week_of_2026-02-23/deliverables/Phil_Tassi_Top10_New_2026-02-23.xlsx
+++ b/results/For_Others/Phil_Tassi/Week_of_2026-02-23/deliverables/Phil_Tassi_Top10_New_2026-02-23.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Job Search Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$5:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Search Results'!$A$5:$N$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -62,11 +62,11 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -81,11 +81,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,11 +120,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -152,9 +153,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -542,27 +540,28 @@
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Phil Tassi — Top 10 New Opportunities</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Week of February 23, 2026  |  Prepared by Joey Clark</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>10 jobs  |  Score range: 72-87  |  Avg: 79.7  |  10 NEW, 0 REPEAT</t>
-        </is>
-      </c>
-    </row>
+          <t>10 jobs  |  Score range: 71-78  |  Avg: 75  |  10 NEW, 0 REPEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -641,27 +640,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>87</v>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Fintech infrastructure partnerships at Plaid. GTM partnerships team unlocks 'one to many' customer relationships. Fintech sector is a perfect match. London office available (36/40 skills, 35/35 industry, 16/25 experience).</t>
+          <t>CoS Product at leading neobank. Product strategy focus with massive scope. Fintech sector perfect (26/40 skills, 35/35 industry, 17/25 experience).</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>Monzo</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Partnerships Account Executive - Enterprise</t>
+          <t>Chief of Staff, Product</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Fintech/Payments Infrastructure</t>
+          <t>Fintech/Banking</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -686,12 +687,12 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>GTM Partnerships team role unlocking one-to-many customer relationships with technology platforms. Plaid offices in San Francisco, New York, Washington DC, London, and Amsterdam.</t>
+          <t>Chief of Staff, Product at Monzo. Lead product strategy with massive scope at the UK's leading digital bank.</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/plaid/b134ba8a-eac5-4271-a279-3ed0176b24de</t>
+          <t>https://boards.greenhouse.io/monzo/jobs/4589197</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
@@ -701,7 +702,7 @@
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
@@ -711,27 +712,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>84</v>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>First Revenue Partnerships hire at leading AI voice company. Builder role perfectly matches zero-to-one experience. AI sector is high-growth. London office available (36/40 skills, 28/35 industry, 20/25 experience).</t>
+          <t>CoS to CEO at legaltech matches operator profile. £110-160K excellent comp. AI-first company is modern (36/40 skills, 20/35 industry, 22/25 experience).</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Lawhive</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Revenue Partnerships</t>
+          <t>Chief of Staff to the CEO</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>AI/Voice Tech</t>
+          <t>LegalTech/AI</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -746,22 +749,22 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Remote-Global</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£110,000-£160,000 + share options</t>
         </is>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>First Revenue Partnerships hire at ElevenLabs, the leading AI voice technology company. Build partnerships function from scratch. Optional offices in London, New York, San Francisco.</t>
+          <t>CEO's core partner ensuring organisation runs with clarity, discipline and focus. AI operating system reinventing legal industry. 3 days/week on-site.</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/elevenlabs/708b7152-f22a-4531-94a9-0f91cc0c1a70</t>
+          <t>https://jobs.ashbyhq.com/lawhive/d579d249-abef-4972-8c6c-63be5af18b34</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -781,27 +784,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>82</v>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Insurtech/fintech platform CoS role. High-trust role directly with CEO driving alignment and execution. Fintech-adjacent sector strongly aligns (34/40 skills, 28/35 industry, 20/25 experience).</t>
+          <t>VC partnerships matches Phil's VC background. Founding EMEA role. Security/compliance SaaS growing (36/40 skills, 22/35 industry, 20/25 experience).</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Bjak</t>
+          <t>Vanta</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Chief of Staff - UK</t>
+          <t>Strategic Venture Capital Partnerships Manager</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Insurtech/Fintech</t>
+          <t>Security/Compliance SaaS</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -826,12 +831,12 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>High-trust, high-leverage role working directly with the CEO to drive alignment, clarity, and execution across the organisation. Bjak builds superior application platforms globally.</t>
+          <t>Founding member of Vanta's Venture &amp; Startup Partnerships team in EMEA. Build and scale presence across London startup and VC ecosystem.</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/bjakcareer/0fda5dff-ed04-4e75-a6bc-939535751cf8</t>
+          <t>https://jobs.ashbyhq.com/vanta/4e32f84c-84c5-45a6-a8b5-2b3f71235286</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -851,27 +856,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>82</v>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Fintech AI financial assistant CoS role. Direct fintech sector alignment. Leadership team coordination matches operator profile. Hybrid London works well (32/40 skills, 30/35 industry, 20/25 experience).</t>
+          <t>BD at homebuying fintech. Financial services sector partially aligns. Regional scope manageable (32/40 skills, 28/35 industry, 16/25 experience).</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Gen H</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Chief of Staff</t>
+          <t>Business Development Manager (London &amp; South East)</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Fintech/AI</t>
+          <t>Fintech/Mortgage</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -896,12 +903,12 @@
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>Bring the leadership team together and run team meetings in lieu of the CEO. Cleo is an AI-powered financial assistant. Hybrid-first role, London office 1-2 times a week.</t>
+          <t>BD Manager at Gen H, rebuilding the homebuying process. Focused on London and South East region.</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/jobs/view/chief-of-staff-at-cleo-3772186729</t>
+          <t>https://boards.greenhouse.io/generationhome/jobs/4279993101</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -911,7 +918,7 @@
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
@@ -921,27 +928,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>80</v>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Senior partnerships leader for EMEA at e-commerce platform. Director-level role matches VP seniority. Strategy and execution for high-impact partner relationships (38/40 skills, 20/35 industry, 22/25 experience).</t>
+          <t>News partnerships at OpenAI. AI sector strong. EMEA scope. Partnership management matches but news-specific (30/40 skills, 28/35 industry, 18/25 experience).</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Director of Partnerships - EMEA</t>
+          <t>Partner Manager, News - EMEA</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>E-commerce Tech</t>
+          <t>AI/Technology</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -966,12 +975,12 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Accelerate presence and pipeline across Europe through high-impact partner relationships. Lead strategy and execution for partnerships in EMEA. London office-based.</t>
+          <t>Build and nurture relationships with news publishing partners through 1:1 interactions and industry programs.</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/pattern/fc621c26-c2ef-40bf-9fb4-3fee3d341436</t>
+          <t>https://jobs.ashbyhq.com/openai/77a2ec4a-10ee-4c7e-b05f-881348b9b41f</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
@@ -981,7 +990,7 @@
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Ashby</t>
         </is>
       </c>
     </row>
@@ -991,32 +1000,34 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>78</v>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>CEO's core partner in ensuring organisational clarity, discipline and focus. Legal tech sector is adjacent to fintech. Strong compensation range (36/40 skills, 20/35 industry, 22/25 experience).</t>
+          <t>Defense/autonomy BD at Applied Intuition. DC location strong. Defense tech partially aligned (34/40 skills, 20/35 industry, 20/25 experience).</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Lawhive</t>
+          <t>Applied Intuition</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Chief of Staff to CEO</t>
+          <t>Business Development Growth Lead - Ground/Air Mission Autonomy</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>Legal Tech</t>
+          <t>Defense/Autonomy Tech</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -1031,17 +1042,17 @@
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>£110,000-£160,000 + options</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>CEO's core partner ensuring the organisation runs with clarity, discipline and focus. London/Hybrid 3 days per week on-site. Series A legal tech startup.</t>
+          <t>BD Growth Lead for Ground/Air Mission Autonomy. Driving growth in defense and autonomous systems.</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/lawhive/d579d249-abef-4972-8c6c-63be5af18b34</t>
+          <t>https://boards.greenhouse.io/appliedintuition/jobs/6547513002</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1051,7 +1062,7 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
@@ -1061,32 +1072,34 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>78</v>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Build partnerships with news publishing partners at leading AI company. Strong sector with high growth. EMEA scope matches London base (32/40 skills, 28/35 industry, 18/25 experience).</t>
+          <t>VC partnerships at Deel matches Phil's VC background. HR/payroll unicorn. Remote-first (34/40 skills, 22/35 industry, 18/25 experience).</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Partner Manager - News EMEA</t>
+          <t>Partnerships Manager, Venture Capital</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>AI/Technology</t>
+          <t>HR Tech/Payroll</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote-Global</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1096,7 +1109,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote-Global</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1106,12 +1119,12 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Build and nurture relationships with news publishing partners through 1:1 interactions, industry programs, and other partnerships at OpenAI. EMEA focus.</t>
+          <t>Partnerships Manager in Venture Capital team at Deel, managing VC and startup ecosystem relationships.</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/77a2ec4a-10ee-4c7e-b05f-881348b9b41f</t>
+          <t>https://jobs.ashbyhq.com/deel/90aefa1d-30b5-4b43-82c2-53348fbc64b9</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1131,32 +1144,34 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>78</v>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Partnerships sales at leading fintech. Broker/white-label models align with banking experience. Fintech/payments sector is excellent fit (32/40 skills, 32/35 industry, 14/25 experience).</t>
+          <t>VP of partnerships at civic tech. DC likely location. Government sector less aligned but partnerships match (36/40 skills, 15/35 industry, 22/25 experience).</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Ebury</t>
+          <t>CivicMarketplace</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Sales Executive - Partnerships</t>
+          <t>VP of Partnerships</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Fintech/Payments</t>
+          <t>GovTech/Civic</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1176,12 +1191,12 @@
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>Expand Partnerships Sales Team managing partners through introductory broker agreements and white-label solutions. Ebury has 1,700+ staff across 25+ countries worldwide.</t>
+          <t>Build trusted relationships with associations and local government leaders. Turn opportunities into impact and revenue.</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/ebury/jobs/4598559101</t>
+          <t>https://jobs.ashbyhq.com/civicmarketplace/1a1b5b1f-b702-4e62-927a-b6030205b371</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1191,7 +1206,7 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Ashby</t>
         </is>
       </c>
     </row>
@@ -1201,27 +1216,29 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>76</v>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Director-level agency partnerships at martech platform. Strategy and execution for scaling agency ecosystem. London hub available (38/40 skills, 18/35 industry, 20/25 experience).</t>
+          <t>Defense/maritime BD in London. Strong seniority match. Defense tech partially aligned (34/40 skills, 18/35 industry, 20/25 experience).</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Attentive</t>
+          <t>Saronic Technologies</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Director - Partnerships (Agency Partners)</t>
+          <t>Business Development - London</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Martech/Communications</t>
+          <t>Defense/Maritime Tech</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -1246,12 +1263,12 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Director of Agency Growth Partnerships, owning strategy and execution for scaling agency ecosystem. Employee hubs in New York City, San Francisco, London, and Sydney.</t>
+          <t>Drive growth by identifying new opportunities in UK and EU. Proven experience in defense, maritime, or technology BD.</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/attentive/2a6e1948-6fbd-4f89-8bb5-12058a67eb02</t>
+          <t>https://jobs.lever.co/saronic/1afc5730-44dd-412b-9f38-81484276b466</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1271,32 +1288,34 @@
           <t>NEW</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>72</v>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Chief of Staff to CRO at martech platform. Strategy, operations, and program leadership blend. London hub available. 5-8+ years experience required (34/40 skills, 18/35 industry, 20/25 experience).</t>
+          <t>Banking infrastructure strategic partnerships. Fintech perfectly aligned but likely SF/NYC-based (36/40 skills, 35/35 industry, 0/25 experience - location uncertain).</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Attentive</t>
+          <t>Column</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Chief of Staff - CRO</t>
+          <t>Strategic Partnerships Lead</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Martech/Communications</t>
+          <t>Fintech/Banking Infrastructure</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1316,12 +1335,12 @@
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>Chief of Staff to the Chief Revenue Officer. Drive alignment, operating rigor, and execution across end-to-end Revenue organization. Attend weekly C-Level Executive meetings and quarterly Board Meetings.</t>
+          <t>Strategic Partnerships Lead at Column, a bank and software company built from the ground up for builders.</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/attentive/f470da25-9907-48a1-bb13-a300ab16ee4e</t>
+          <t>https://jobs.ashbyhq.com/column/83c71171-e327-45e2-8b58-cfe5ee16209a</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1331,12 +1350,12 @@
       </c>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Ashby</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Score Key: 🟢 90+ Elite | 🔵 80-89 Strong | 🟡 70-79 Good | 🔴 Below 70</t>
         </is>
